--- a/VerveStacks_ZWE/SysSettings.xlsx
+++ b/VerveStacks_ZWE/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZWE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFC8A15-8184-4EEC-BA20-B350048CF0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A05052A-636A-4E01-B6E1-7C5DE7FE34C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ZWE/SysSettings.xlsx
+++ b/VerveStacks_ZWE/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZWE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A05052A-636A-4E01-B6E1-7C5DE7FE34C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4B392D-D629-4C32-BE84-B791BD8CDBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>

--- a/VerveStacks_ZWE/SysSettings.xlsx
+++ b/VerveStacks_ZWE/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZWE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4B392D-D629-4C32-BE84-B791BD8CDBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A10AB55-2D69-4E4F-A858-CF299F822A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
